--- a/assets/excel/2025_4-2-1.xlsx
+++ b/assets/excel/2025_4-2-1.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\Hannover\Dez15_Uebergreifende_Analysen\Projekte\Integrationsmonitoring\github\MT_Site\assets\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\Hannover\Dez15_Uebergreifende_Analysen\Projekte\Integrationsmonitoring\Schlesier\MT_Site\assets\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AE22BF74-8745-4F4F-A1E4-B9ED26A457CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC42AC04-2601-4617-90EC-7720B9F79229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{F00CF707-31DB-41A0-9AE6-C8AE49075CB7}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,6 +28,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -159,7 +162,7 @@
     <t>Migration und Teilhabe in Niedersachsen - Integrationsmonitoring 2025</t>
   </si>
   <si>
-    <t>© Landesamt für Statistik Niedersachsen, Hannover 2025,                                                             </t>
+    <t>© Landesamt für Statistik Niedersachsen, Hannover 2026,                                                             </t>
   </si>
 </sst>
 </file>
@@ -428,107 +431,107 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -898,1724 +901,1724 @@
       <c r="J5" s="5"/>
     </row>
     <row r="6" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="27"/>
+      <c r="L6" s="27"/>
     </row>
     <row r="7" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="9"/>
-      <c r="C7" s="10" t="s">
+      <c r="B7" s="24"/>
+      <c r="C7" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="12"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="13" t="s">
+      <c r="E7" s="32"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="14"/>
+      <c r="H7" s="37"/>
+      <c r="I7" s="37"/>
+      <c r="J7" s="37"/>
+      <c r="K7" s="37"/>
+      <c r="L7" s="38"/>
     </row>
     <row r="8" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="9"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="11" t="s">
+      <c r="B8" s="24"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="H8" s="12"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="13" t="s">
+      <c r="H8" s="32"/>
+      <c r="I8" s="23"/>
+      <c r="J8" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="K8" s="13"/>
-      <c r="L8" s="14"/>
+      <c r="K8" s="37"/>
+      <c r="L8" s="38"/>
     </row>
     <row r="9" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="9"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="14"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="37"/>
+      <c r="K9" s="37"/>
+      <c r="L9" s="38"/>
     </row>
     <row r="10" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="9"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="21" t="s">
+      <c r="B10" s="24"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="E10" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="F10" s="22" t="s">
+      <c r="F10" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="G10" s="22" t="s">
+      <c r="G10" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="H10" s="22" t="s">
+      <c r="H10" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I10" s="22" t="s">
+      <c r="I10" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="J10" s="22" t="s">
+      <c r="J10" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="K10" s="22" t="s">
+      <c r="K10" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="L10" s="23" t="s">
+      <c r="L10" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="20"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="25" t="s">
+      <c r="B11" s="25"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="14"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="37"/>
+      <c r="G11" s="37"/>
+      <c r="H11" s="37"/>
+      <c r="I11" s="37"/>
+      <c r="J11" s="37"/>
+      <c r="K11" s="37"/>
+      <c r="L11" s="38"/>
     </row>
     <row r="12" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="26">
+      <c r="B12" s="9">
         <v>1</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="9">
         <v>2</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="9">
         <v>3</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="9">
         <v>4</v>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="9">
         <v>5</v>
       </c>
-      <c r="G12" s="26">
+      <c r="G12" s="9">
         <v>6</v>
       </c>
-      <c r="H12" s="26">
+      <c r="H12" s="9">
         <v>7</v>
       </c>
-      <c r="I12" s="26">
+      <c r="I12" s="9">
         <v>8</v>
       </c>
-      <c r="J12" s="26">
+      <c r="J12" s="9">
         <v>9</v>
       </c>
-      <c r="K12" s="26">
+      <c r="K12" s="9">
         <v>10</v>
       </c>
-      <c r="L12" s="26">
+      <c r="L12" s="9">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="9">
         <v>2024</v>
       </c>
-      <c r="D13" s="39">
+      <c r="D13" s="21">
         <v>24.172010483896035</v>
       </c>
-      <c r="E13" s="39">
+      <c r="E13" s="21">
         <v>26.244262622231091</v>
       </c>
-      <c r="F13" s="39">
+      <c r="F13" s="21">
         <v>21.937137809948513</v>
       </c>
-      <c r="G13" s="39">
+      <c r="G13" s="21">
         <v>43.904969048017399</v>
       </c>
-      <c r="H13" s="39">
+      <c r="H13" s="21">
         <v>48.488696977393957</v>
       </c>
-      <c r="I13" s="39">
+      <c r="I13" s="21">
         <v>38.798896512697176</v>
       </c>
-      <c r="J13" s="39">
+      <c r="J13" s="21">
         <v>15.324710401536521</v>
       </c>
-      <c r="K13" s="39">
+      <c r="K13" s="21">
         <v>16.049706070659447</v>
       </c>
-      <c r="L13" s="39">
+      <c r="L13" s="21">
         <v>14.553001672758811</v>
       </c>
     </row>
     <row r="14" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="9">
         <v>2024</v>
       </c>
-      <c r="D14" s="39">
+      <c r="D14" s="21">
         <v>46.383988231515922</v>
       </c>
-      <c r="E14" s="39">
+      <c r="E14" s="21">
         <v>47.936539612851725</v>
       </c>
-      <c r="F14" s="39">
+      <c r="F14" s="21">
         <v>44.707985954027443</v>
       </c>
-      <c r="G14" s="39">
+      <c r="G14" s="21">
         <v>31.085829011209636</v>
       </c>
-      <c r="H14" s="39">
+      <c r="H14" s="21">
         <v>30.041910083820174</v>
       </c>
-      <c r="I14" s="39">
+      <c r="I14" s="21">
         <v>32.248709061328427</v>
       </c>
-      <c r="J14" s="39">
+      <c r="J14" s="21">
         <v>53.244102995018295</v>
       </c>
-      <c r="K14" s="39">
+      <c r="K14" s="21">
         <v>56.134683662184969</v>
       </c>
-      <c r="L14" s="39">
+      <c r="L14" s="21">
         <v>50.167275881296078</v>
       </c>
     </row>
     <row r="15" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="27" t="s">
+      <c r="B15" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="26">
+      <c r="C15" s="9">
         <v>2024</v>
       </c>
-      <c r="D15" s="39">
+      <c r="D15" s="21">
         <v>29.444001284588055</v>
       </c>
-      <c r="E15" s="39">
+      <c r="E15" s="21">
         <v>25.82119337457593</v>
       </c>
-      <c r="F15" s="39">
+      <c r="F15" s="21">
         <v>33.354876236024047</v>
       </c>
-      <c r="G15" s="39">
+      <c r="G15" s="21">
         <v>25.009201940772961</v>
       </c>
-      <c r="H15" s="39">
+      <c r="H15" s="21">
         <v>21.46939293878588</v>
       </c>
-      <c r="I15" s="39">
+      <c r="I15" s="21">
         <v>28.952394425974393</v>
       </c>
-      <c r="J15" s="39">
+      <c r="J15" s="21">
         <v>31.432687113618631</v>
       </c>
-      <c r="K15" s="39">
+      <c r="K15" s="21">
         <v>27.815610267155577</v>
       </c>
-      <c r="L15" s="39">
+      <c r="L15" s="21">
         <v>35.282820147450593</v>
       </c>
     </row>
     <row r="16" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="27" t="s">
+      <c r="B16" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="26">
+      <c r="C16" s="9">
         <v>2024</v>
       </c>
-      <c r="D16" s="39">
+      <c r="D16" s="21">
         <v>27.489694298191914</v>
       </c>
-      <c r="E16" s="39">
+      <c r="E16" s="21">
         <v>29.002896152254863</v>
       </c>
-      <c r="F16" s="39">
+      <c r="F16" s="21">
         <v>25.864076025991068</v>
       </c>
-      <c r="G16" s="39">
+      <c r="G16" s="21">
         <v>46.127236187526769</v>
       </c>
-      <c r="H16" s="39">
+      <c r="H16" s="21">
         <v>47.952888390353337</v>
       </c>
-      <c r="I16" s="39">
+      <c r="I16" s="21">
         <v>44.079407241716758</v>
       </c>
-      <c r="J16" s="39">
+      <c r="J16" s="21">
         <v>19.129059437406688</v>
       </c>
-      <c r="K16" s="39">
+      <c r="K16" s="21">
         <v>20.242005185825409</v>
       </c>
-      <c r="L16" s="39">
+      <c r="L16" s="21">
         <v>17.956346194711756</v>
       </c>
     </row>
     <row r="17" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="28" t="s">
+      <c r="B17" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="26">
+      <c r="C17" s="9">
         <v>2024</v>
       </c>
-      <c r="D17" s="39">
+      <c r="D17" s="21">
         <v>46.682788457613981</v>
       </c>
-      <c r="E17" s="39">
+      <c r="E17" s="21">
         <v>47.504777666134721</v>
       </c>
-      <c r="F17" s="39">
+      <c r="F17" s="21">
         <v>45.799733316401039</v>
       </c>
-      <c r="G17" s="39">
+      <c r="G17" s="21">
         <v>29.894903304450963</v>
       </c>
-      <c r="H17" s="39">
+      <c r="H17" s="21">
         <v>29.799962609833614</v>
       </c>
-      <c r="I17" s="39">
+      <c r="I17" s="21">
         <v>30.00139801481896</v>
       </c>
-      <c r="J17" s="39">
+      <c r="J17" s="21">
         <v>54.215015299108657</v>
       </c>
-      <c r="K17" s="39">
+      <c r="K17" s="21">
         <v>55.690002881014109</v>
       </c>
-      <c r="L17" s="39">
+      <c r="L17" s="21">
         <v>52.660817825809779</v>
       </c>
     </row>
     <row r="18" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="27" t="s">
+      <c r="B18" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="26">
+      <c r="C18" s="9">
         <v>2024</v>
       </c>
-      <c r="D18" s="39">
+      <c r="D18" s="21">
         <v>25.826496877678462</v>
       </c>
-      <c r="E18" s="39">
+      <c r="E18" s="21">
         <v>23.492326181610419</v>
       </c>
-      <c r="F18" s="39">
+      <c r="F18" s="21">
         <v>28.33619065760789</v>
       </c>
-      <c r="G18" s="39">
+      <c r="G18" s="21">
         <v>23.981155075280867</v>
       </c>
-      <c r="H18" s="39">
+      <c r="H18" s="21">
         <v>22.247148999813053</v>
       </c>
-      <c r="I18" s="39">
+      <c r="I18" s="21">
         <v>25.926184817559069</v>
       </c>
-      <c r="J18" s="39">
+      <c r="J18" s="21">
         <v>26.655925263484654</v>
       </c>
-      <c r="K18" s="39">
+      <c r="K18" s="21">
         <v>24.067991933160474</v>
       </c>
-      <c r="L18" s="39">
+      <c r="L18" s="21">
         <v>29.382835979478461</v>
       </c>
     </row>
     <row r="19" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="27" t="s">
+      <c r="B19" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="26">
+      <c r="C19" s="9">
         <v>2023</v>
       </c>
-      <c r="D19" s="39">
+      <c r="D19" s="21">
         <v>26.197855587200536</v>
       </c>
-      <c r="E19" s="39">
+      <c r="E19" s="21">
         <v>27.425752542031617</v>
       </c>
-      <c r="F19" s="39">
+      <c r="F19" s="21">
         <v>24.867470930866727</v>
       </c>
-      <c r="G19" s="39">
+      <c r="G19" s="21">
         <v>46.392761066275376</v>
       </c>
-      <c r="H19" s="39">
+      <c r="H19" s="21">
         <v>48.949524312896401</v>
       </c>
-      <c r="I19" s="39">
+      <c r="I19" s="21">
         <v>43.523392896863648</v>
       </c>
-      <c r="J19" s="39">
+      <c r="J19" s="21">
         <v>17.555060480555014</v>
       </c>
-      <c r="K19" s="39">
+      <c r="K19" s="21">
         <v>17.990674505488137</v>
       </c>
-      <c r="L19" s="39">
+      <c r="L19" s="21">
         <v>17.090133531157271</v>
       </c>
     </row>
     <row r="20" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="28" t="s">
+      <c r="B20" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="26">
+      <c r="C20" s="9">
         <v>2023</v>
       </c>
-      <c r="D20" s="39">
+      <c r="D20" s="21">
         <v>46.473446138381632</v>
       </c>
-      <c r="E20" s="39">
+      <c r="E20" s="21">
         <v>48.414376321353068</v>
       </c>
-      <c r="F20" s="39">
+      <c r="F20" s="21">
         <v>44.370514190972749</v>
       </c>
-      <c r="G20" s="39">
+      <c r="G20" s="21">
         <v>29.448345735946614</v>
       </c>
-      <c r="H20" s="39">
+      <c r="H20" s="21">
         <v>29.770084566596193</v>
       </c>
-      <c r="I20" s="39">
+      <c r="I20" s="21">
         <v>29.08726922221398</v>
       </c>
-      <c r="J20" s="39">
+      <c r="J20" s="21">
         <v>53.759662684469433</v>
       </c>
-      <c r="K20" s="39">
+      <c r="K20" s="21">
         <v>56.590112658924383</v>
       </c>
-      <c r="L20" s="39">
+      <c r="L20" s="21">
         <v>50.738748763600405</v>
       </c>
     </row>
     <row r="21" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="27" t="s">
+      <c r="B21" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="26">
+      <c r="C21" s="9">
         <v>2023</v>
       </c>
-      <c r="D21" s="39">
+      <c r="D21" s="21">
         <v>27.328698274417828</v>
       </c>
-      <c r="E21" s="39">
+      <c r="E21" s="21">
         <v>24.159871136615322</v>
       </c>
-      <c r="F21" s="39">
+      <c r="F21" s="21">
         <v>30.762014878160514</v>
       </c>
-      <c r="G21" s="39">
+      <c r="G21" s="21">
         <v>24.16238689166055</v>
       </c>
-      <c r="H21" s="39">
+      <c r="H21" s="21">
         <v>21.286997885835092</v>
       </c>
-      <c r="I21" s="39">
+      <c r="I21" s="21">
         <v>27.389337880922366</v>
       </c>
-      <c r="J21" s="39">
+      <c r="J21" s="21">
         <v>28.685276834975554</v>
       </c>
-      <c r="K21" s="39">
+      <c r="K21" s="21">
         <v>25.422108951895506</v>
       </c>
-      <c r="L21" s="39">
+      <c r="L21" s="21">
         <v>32.168026706231458</v>
       </c>
     </row>
     <row r="22" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="27" t="s">
+      <c r="B22" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="26">
+      <c r="C22" s="9">
         <v>2022</v>
       </c>
-      <c r="D22" s="39">
+      <c r="D22" s="21">
         <v>27.489694298191914</v>
       </c>
-      <c r="E22" s="39">
+      <c r="E22" s="21">
         <v>29.002896152254863</v>
       </c>
-      <c r="F22" s="39">
+      <c r="F22" s="21">
         <v>25.864076025991068</v>
       </c>
-      <c r="G22" s="39">
+      <c r="G22" s="21">
         <v>46.127236187526769</v>
       </c>
-      <c r="H22" s="39">
+      <c r="H22" s="21">
         <v>47.952888390353337</v>
       </c>
-      <c r="I22" s="39">
+      <c r="I22" s="21">
         <v>44.079407241716758</v>
       </c>
-      <c r="J22" s="39">
+      <c r="J22" s="21">
         <v>19.129059437406688</v>
       </c>
-      <c r="K22" s="39">
+      <c r="K22" s="21">
         <v>20.242005185825409</v>
       </c>
-      <c r="L22" s="39">
+      <c r="L22" s="21">
         <v>17.956346194711756</v>
       </c>
     </row>
     <row r="23" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="28" t="s">
+      <c r="B23" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C23" s="26">
+      <c r="C23" s="9">
         <v>2022</v>
       </c>
-      <c r="D23" s="39">
+      <c r="D23" s="21">
         <v>46.682788457613981</v>
       </c>
-      <c r="E23" s="39">
+      <c r="E23" s="21">
         <v>47.504777666134721</v>
       </c>
-      <c r="F23" s="39">
+      <c r="F23" s="21">
         <v>45.799733316401039</v>
       </c>
-      <c r="G23" s="39">
+      <c r="G23" s="21">
         <v>29.894903304450963</v>
       </c>
-      <c r="H23" s="39">
+      <c r="H23" s="21">
         <v>29.799962609833614</v>
       </c>
-      <c r="I23" s="39">
+      <c r="I23" s="21">
         <v>30.00139801481896</v>
       </c>
-      <c r="J23" s="39">
+      <c r="J23" s="21">
         <v>54.215015299108657</v>
       </c>
-      <c r="K23" s="39">
+      <c r="K23" s="21">
         <v>55.690002881014109</v>
       </c>
-      <c r="L23" s="39">
+      <c r="L23" s="21">
         <v>52.660817825809779</v>
       </c>
     </row>
     <row r="24" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="27" t="s">
+      <c r="B24" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="26">
+      <c r="C24" s="9">
         <v>2022</v>
       </c>
-      <c r="D24" s="39">
+      <c r="D24" s="21">
         <v>25.826496877678462</v>
       </c>
-      <c r="E24" s="39">
+      <c r="E24" s="21">
         <v>23.492326181610419</v>
       </c>
-      <c r="F24" s="39">
+      <c r="F24" s="21">
         <v>28.33619065760789</v>
       </c>
-      <c r="G24" s="39">
+      <c r="G24" s="21">
         <v>23.981155075280867</v>
       </c>
-      <c r="H24" s="39">
+      <c r="H24" s="21">
         <v>22.247148999813053</v>
       </c>
-      <c r="I24" s="39">
+      <c r="I24" s="21">
         <v>25.926184817559069</v>
       </c>
-      <c r="J24" s="39">
+      <c r="J24" s="21">
         <v>26.655925263484654</v>
       </c>
-      <c r="K24" s="39">
+      <c r="K24" s="21">
         <v>24.067991933160474</v>
       </c>
-      <c r="L24" s="39">
+      <c r="L24" s="21">
         <v>29.382835979478461</v>
       </c>
     </row>
     <row r="25" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="27" t="s">
+      <c r="B25" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C25" s="26">
+      <c r="C25" s="9">
         <v>2021</v>
       </c>
-      <c r="D25" s="29">
+      <c r="D25" s="12">
         <v>25.902993839243404</v>
       </c>
-      <c r="E25" s="29">
+      <c r="E25" s="12">
         <v>28.162686214235038</v>
       </c>
-      <c r="F25" s="29">
+      <c r="F25" s="12">
         <v>23.427177339263356</v>
       </c>
-      <c r="G25" s="29">
+      <c r="G25" s="12">
         <v>44.901561439239643</v>
       </c>
-      <c r="H25" s="29">
+      <c r="H25" s="12">
         <v>47.693755883275813</v>
       </c>
-      <c r="I25" s="29">
+      <c r="I25" s="12">
         <v>41.611829944547132</v>
       </c>
-      <c r="J25" s="29">
+      <c r="J25" s="12">
         <v>17.624175369050086</v>
       </c>
-      <c r="K25" s="29">
+      <c r="K25" s="12">
         <v>19.223256348385615</v>
       </c>
-      <c r="L25" s="29">
+      <c r="L25" s="12">
         <v>15.926693907422088</v>
       </c>
     </row>
     <row r="26" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="28" t="s">
+      <c r="B26" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="26">
+      <c r="C26" s="9">
         <v>2021</v>
       </c>
-      <c r="D26" s="29">
+      <c r="D26" s="12">
         <v>49.419982280098083</v>
       </c>
-      <c r="E26" s="29">
+      <c r="E26" s="12">
         <v>49.404902656262308</v>
       </c>
-      <c r="F26" s="29">
+      <c r="F26" s="12">
         <v>49.436504166846582</v>
       </c>
-      <c r="G26" s="29">
+      <c r="G26" s="12">
         <v>32.861507128309569</v>
       </c>
-      <c r="H26" s="29">
+      <c r="H26" s="12">
         <v>32.212111703796673</v>
       </c>
-      <c r="I26" s="29">
+      <c r="I26" s="12">
         <v>33.626617375231049</v>
       </c>
-      <c r="J26" s="29">
+      <c r="J26" s="12">
         <v>56.635505724343993</v>
       </c>
-      <c r="K26" s="29">
+      <c r="K26" s="12">
         <v>57.276226588532687</v>
       </c>
-      <c r="L26" s="29">
+      <c r="L26" s="12">
         <v>55.955357687381834</v>
       </c>
     </row>
     <row r="27" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="27" t="s">
+      <c r="B27" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="26">
+      <c r="C27" s="9">
         <v>2021</v>
       </c>
-      <c r="D27" s="29">
+      <c r="D27" s="12">
         <v>24.67702388065852</v>
       </c>
-      <c r="E27" s="29">
+      <c r="E27" s="12">
         <v>22.430440608496884</v>
       </c>
-      <c r="F27" s="29">
+      <c r="F27" s="12">
         <v>27.136318493890066</v>
       </c>
-      <c r="G27" s="29">
+      <c r="G27" s="12">
         <v>22.236931432450781</v>
       </c>
-      <c r="H27" s="29">
+      <c r="H27" s="12">
         <v>20.094132412927522</v>
       </c>
-      <c r="I27" s="29">
+      <c r="I27" s="12">
         <v>24.761552680221811</v>
       </c>
-      <c r="J27" s="29">
+      <c r="J27" s="12">
         <v>25.740318906605925</v>
       </c>
-      <c r="K27" s="29">
+      <c r="K27" s="12">
         <v>23.500517063081698</v>
       </c>
-      <c r="L27" s="29">
+      <c r="L27" s="12">
         <v>28.117948405196071</v>
       </c>
     </row>
     <row r="28" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="27" t="s">
+      <c r="B28" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="26">
+      <c r="C28" s="9">
         <v>2019</v>
       </c>
-      <c r="D28" s="29">
+      <c r="D28" s="12">
         <v>21.64</v>
       </c>
-      <c r="E28" s="29">
+      <c r="E28" s="12">
         <v>23.17</v>
       </c>
-      <c r="F28" s="29">
+      <c r="F28" s="12">
         <v>19.91</v>
       </c>
-      <c r="G28" s="29">
+      <c r="G28" s="12">
         <v>39.78</v>
       </c>
-      <c r="H28" s="29">
+      <c r="H28" s="12">
         <v>42.48</v>
       </c>
-      <c r="I28" s="29">
+      <c r="I28" s="12">
         <v>36.43</v>
       </c>
-      <c r="J28" s="29">
+      <c r="J28" s="12">
         <v>14.03</v>
       </c>
-      <c r="K28" s="29">
+      <c r="K28" s="12">
         <v>14.58</v>
       </c>
-      <c r="L28" s="29">
+      <c r="L28" s="12">
         <v>13.44</v>
       </c>
     </row>
     <row r="29" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="28" t="s">
+      <c r="B29" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="26">
+      <c r="C29" s="9">
         <v>2019</v>
       </c>
-      <c r="D29" s="29">
+      <c r="D29" s="12">
         <v>46.87</v>
       </c>
-      <c r="E29" s="29">
+      <c r="E29" s="12">
         <v>48.72</v>
       </c>
-      <c r="F29" s="29">
+      <c r="F29" s="12">
         <v>44.77</v>
       </c>
-      <c r="G29" s="29">
+      <c r="G29" s="12">
         <v>34.21</v>
       </c>
-      <c r="H29" s="29">
+      <c r="H29" s="12">
         <v>34.56</v>
       </c>
-      <c r="I29" s="29">
+      <c r="I29" s="12">
         <v>33.770000000000003</v>
       </c>
-      <c r="J29" s="29">
+      <c r="J29" s="12">
         <v>52.18</v>
       </c>
-      <c r="K29" s="29">
+      <c r="K29" s="12">
         <v>55.02</v>
       </c>
-      <c r="L29" s="29">
+      <c r="L29" s="12">
         <v>49.09</v>
       </c>
     </row>
     <row r="30" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="27" t="s">
+      <c r="B30" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C30" s="26">
+      <c r="C30" s="9">
         <v>2019</v>
       </c>
-      <c r="D30" s="29">
+      <c r="D30" s="12">
         <v>31.49</v>
       </c>
-      <c r="E30" s="29">
+      <c r="E30" s="12">
         <v>28.11</v>
       </c>
-      <c r="F30" s="29">
+      <c r="F30" s="12">
         <v>35.31</v>
       </c>
-      <c r="G30" s="29">
+      <c r="G30" s="12">
         <v>26.02</v>
       </c>
-      <c r="H30" s="29">
+      <c r="H30" s="12">
         <v>22.97</v>
       </c>
-      <c r="I30" s="29">
+      <c r="I30" s="12">
         <v>29.8</v>
       </c>
-      <c r="J30" s="29">
+      <c r="J30" s="12">
         <v>33.79</v>
       </c>
-      <c r="K30" s="29">
+      <c r="K30" s="12">
         <v>30.4</v>
       </c>
-      <c r="L30" s="29">
+      <c r="L30" s="12">
         <v>37.47</v>
       </c>
     </row>
     <row r="31" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="27" t="s">
+      <c r="B31" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="30">
+      <c r="C31" s="13">
         <v>2018</v>
       </c>
-      <c r="D31" s="29">
+      <c r="D31" s="12">
         <v>21.82</v>
       </c>
-      <c r="E31" s="29">
+      <c r="E31" s="12">
         <v>23.59</v>
       </c>
-      <c r="F31" s="29">
+      <c r="F31" s="12">
         <v>19.86</v>
       </c>
-      <c r="G31" s="29">
+      <c r="G31" s="12">
         <v>38.44</v>
       </c>
-      <c r="H31" s="29">
+      <c r="H31" s="12">
         <v>41.18</v>
       </c>
-      <c r="I31" s="29">
+      <c r="I31" s="12">
         <v>35.28</v>
       </c>
-      <c r="J31" s="29">
+      <c r="J31" s="12">
         <v>14.77</v>
       </c>
-      <c r="K31" s="29">
+      <c r="K31" s="12">
         <v>15.91</v>
       </c>
-      <c r="L31" s="29">
+      <c r="L31" s="12">
         <v>13.54</v>
       </c>
     </row>
     <row r="32" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="28" t="s">
+      <c r="B32" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C32" s="31">
+      <c r="C32" s="14">
         <v>2018</v>
       </c>
-      <c r="D32" s="29">
+      <c r="D32" s="12">
         <v>48.44</v>
       </c>
-      <c r="E32" s="29">
+      <c r="E32" s="12">
         <v>50.1</v>
       </c>
-      <c r="F32" s="29">
+      <c r="F32" s="12">
         <v>46.61</v>
       </c>
-      <c r="G32" s="29">
+      <c r="G32" s="12">
         <v>36.17</v>
       </c>
-      <c r="H32" s="29">
+      <c r="H32" s="12">
         <v>35.78</v>
       </c>
-      <c r="I32" s="29">
+      <c r="I32" s="12">
         <v>36.61</v>
       </c>
-      <c r="J32" s="29">
+      <c r="J32" s="12">
         <v>53.64</v>
       </c>
-      <c r="K32" s="29">
+      <c r="K32" s="12">
         <v>56.34</v>
       </c>
-      <c r="L32" s="29">
+      <c r="L32" s="12">
         <v>50.72</v>
       </c>
     </row>
     <row r="33" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="27" t="s">
+      <c r="B33" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="30">
+      <c r="C33" s="13">
         <v>2018</v>
       </c>
-      <c r="D33" s="29">
+      <c r="D33" s="12">
         <v>29.74</v>
       </c>
-      <c r="E33" s="29">
+      <c r="E33" s="12">
         <v>26.32</v>
       </c>
-      <c r="F33" s="29">
+      <c r="F33" s="12">
         <v>33.520000000000003</v>
       </c>
-      <c r="G33" s="29">
+      <c r="G33" s="12">
         <v>25.4</v>
       </c>
-      <c r="H33" s="29">
+      <c r="H33" s="12">
         <v>23.04</v>
       </c>
-      <c r="I33" s="29">
+      <c r="I33" s="12">
         <v>28.11</v>
       </c>
-      <c r="J33" s="29">
+      <c r="J33" s="12">
         <v>31.58</v>
       </c>
-      <c r="K33" s="29">
+      <c r="K33" s="12">
         <v>27.75</v>
       </c>
-      <c r="L33" s="29">
+      <c r="L33" s="12">
         <v>35.74</v>
       </c>
     </row>
     <row r="34" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="27" t="s">
+      <c r="B34" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C34" s="30">
+      <c r="C34" s="13">
         <v>2017</v>
       </c>
-      <c r="D34" s="29">
+      <c r="D34" s="12">
         <v>21.83</v>
       </c>
-      <c r="E34" s="29">
+      <c r="E34" s="12">
         <v>23.47</v>
       </c>
-      <c r="F34" s="29">
+      <c r="F34" s="12">
         <v>19.989999999999998</v>
       </c>
-      <c r="G34" s="29">
+      <c r="G34" s="12">
         <v>36.369999999999997</v>
       </c>
-      <c r="H34" s="29">
+      <c r="H34" s="12">
         <v>39.1</v>
       </c>
-      <c r="I34" s="29">
+      <c r="I34" s="12">
         <v>33.03</v>
       </c>
-      <c r="J34" s="29">
+      <c r="J34" s="12">
         <v>15.47</v>
       </c>
-      <c r="K34" s="29">
+      <c r="K34" s="12">
         <v>16.23</v>
       </c>
-      <c r="L34" s="29">
+      <c r="L34" s="12">
         <v>14.64</v>
       </c>
     </row>
     <row r="35" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="28" t="s">
+      <c r="B35" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C35" s="30">
+      <c r="C35" s="13">
         <v>2017</v>
       </c>
-      <c r="D35" s="29">
+      <c r="D35" s="12">
         <v>49.19</v>
       </c>
-      <c r="E35" s="29">
+      <c r="E35" s="12">
         <v>50.81</v>
       </c>
-      <c r="F35" s="29">
+      <c r="F35" s="12">
         <v>47.38</v>
       </c>
-      <c r="G35" s="29">
+      <c r="G35" s="12">
         <v>39.159999999999997</v>
       </c>
-      <c r="H35" s="29">
+      <c r="H35" s="12">
         <v>38.630000000000003</v>
       </c>
-      <c r="I35" s="29">
+      <c r="I35" s="12">
         <v>39.79</v>
       </c>
-      <c r="J35" s="29">
+      <c r="J35" s="12">
         <v>53.59</v>
       </c>
-      <c r="K35" s="29">
+      <c r="K35" s="12">
         <v>56.45</v>
       </c>
-      <c r="L35" s="29">
+      <c r="L35" s="12">
         <v>50.49</v>
       </c>
     </row>
     <row r="36" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="27" t="s">
+      <c r="B36" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C36" s="30">
+      <c r="C36" s="13">
         <v>2017</v>
       </c>
-      <c r="D36" s="29">
+      <c r="D36" s="12">
         <v>28.98</v>
       </c>
-      <c r="E36" s="29">
+      <c r="E36" s="12">
         <v>25.72</v>
       </c>
-      <c r="F36" s="29">
+      <c r="F36" s="12">
         <v>32.630000000000003</v>
       </c>
-      <c r="G36" s="29">
+      <c r="G36" s="12">
         <v>24.48</v>
       </c>
-      <c r="H36" s="29">
+      <c r="H36" s="12">
         <v>22.26</v>
       </c>
-      <c r="I36" s="29">
+      <c r="I36" s="12">
         <v>27.18</v>
       </c>
-      <c r="J36" s="29">
+      <c r="J36" s="12">
         <v>30.95</v>
       </c>
-      <c r="K36" s="29">
+      <c r="K36" s="12">
         <v>27.32</v>
       </c>
-      <c r="L36" s="29">
+      <c r="L36" s="12">
         <v>34.869999999999997</v>
       </c>
     </row>
     <row r="37" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="27" t="s">
+      <c r="B37" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C37" s="30">
+      <c r="C37" s="13">
         <v>2016</v>
       </c>
-      <c r="D37" s="29">
+      <c r="D37" s="12">
         <v>22.14</v>
       </c>
-      <c r="E37" s="29">
+      <c r="E37" s="12">
         <v>23.92</v>
       </c>
-      <c r="F37" s="29">
+      <c r="F37" s="12">
         <v>20.149999999999999</v>
       </c>
-      <c r="G37" s="29">
+      <c r="G37" s="12">
         <v>38.9</v>
       </c>
-      <c r="H37" s="29">
+      <c r="H37" s="12">
         <v>40.369999999999997</v>
       </c>
-      <c r="I37" s="29">
+      <c r="I37" s="12">
         <v>37.090000000000003</v>
       </c>
-      <c r="J37" s="29">
+      <c r="J37" s="12">
         <v>16.14</v>
       </c>
-      <c r="K37" s="29">
+      <c r="K37" s="12">
         <v>17.64</v>
       </c>
-      <c r="L37" s="29">
+      <c r="L37" s="12">
         <v>14.54</v>
       </c>
     </row>
     <row r="38" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="28" t="s">
+      <c r="B38" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C38" s="30">
+      <c r="C38" s="13">
         <v>2016</v>
       </c>
-      <c r="D38" s="29">
+      <c r="D38" s="12">
         <v>50.52</v>
       </c>
-      <c r="E38" s="29">
+      <c r="E38" s="12">
         <v>51.29</v>
       </c>
-      <c r="F38" s="29">
+      <c r="F38" s="12">
         <v>49.65</v>
       </c>
-      <c r="G38" s="29">
+      <c r="G38" s="12">
         <v>37.78</v>
       </c>
-      <c r="H38" s="29">
+      <c r="H38" s="12">
         <v>37.340000000000003</v>
       </c>
-      <c r="I38" s="29">
+      <c r="I38" s="12">
         <v>38.32</v>
       </c>
-      <c r="J38" s="29">
+      <c r="J38" s="12">
         <v>55.07</v>
       </c>
-      <c r="K38" s="29">
+      <c r="K38" s="12">
         <v>56.62</v>
       </c>
-      <c r="L38" s="29">
+      <c r="L38" s="12">
         <v>53.41</v>
       </c>
     </row>
     <row r="39" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="27" t="s">
+      <c r="B39" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C39" s="30">
+      <c r="C39" s="13">
         <v>2016</v>
       </c>
-      <c r="D39" s="29">
+      <c r="D39" s="12">
         <v>27.35</v>
       </c>
-      <c r="E39" s="29">
+      <c r="E39" s="12">
         <v>24.79</v>
       </c>
-      <c r="F39" s="29">
+      <c r="F39" s="12">
         <v>30.2</v>
       </c>
-      <c r="G39" s="29">
+      <c r="G39" s="12">
         <v>23.32</v>
       </c>
-      <c r="H39" s="29">
+      <c r="H39" s="12">
         <v>22.3</v>
       </c>
-      <c r="I39" s="29">
+      <c r="I39" s="12">
         <v>24.59</v>
       </c>
-      <c r="J39" s="29">
+      <c r="J39" s="12">
         <v>28.78</v>
       </c>
-      <c r="K39" s="29">
+      <c r="K39" s="12">
         <v>25.74</v>
       </c>
-      <c r="L39" s="29">
+      <c r="L39" s="12">
         <v>32.06</v>
       </c>
     </row>
     <row r="40" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="27" t="s">
+      <c r="B40" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C40" s="30">
+      <c r="C40" s="13">
         <v>2015</v>
       </c>
-      <c r="D40" s="29">
+      <c r="D40" s="12">
         <v>19.34</v>
       </c>
-      <c r="E40" s="29">
+      <c r="E40" s="12">
         <v>20.13</v>
       </c>
-      <c r="F40" s="29">
+      <c r="F40" s="12">
         <v>18.510000000000002</v>
       </c>
-      <c r="G40" s="29">
+      <c r="G40" s="12">
         <v>35.28</v>
       </c>
-      <c r="H40" s="29">
+      <c r="H40" s="12">
         <v>34.89</v>
       </c>
-      <c r="I40" s="29">
+      <c r="I40" s="12">
         <v>35.659999999999997</v>
       </c>
-      <c r="J40" s="29">
+      <c r="J40" s="12">
         <v>14.59</v>
       </c>
-      <c r="K40" s="29">
+      <c r="K40" s="12">
         <v>15.87</v>
       </c>
-      <c r="L40" s="29">
+      <c r="L40" s="12">
         <v>13.22</v>
       </c>
     </row>
     <row r="41" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="28" t="s">
+      <c r="B41" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C41" s="30">
+      <c r="C41" s="13">
         <v>2015</v>
       </c>
-      <c r="D41" s="29">
+      <c r="D41" s="12">
         <v>51.57</v>
       </c>
-      <c r="E41" s="29">
+      <c r="E41" s="12">
         <v>53.84</v>
       </c>
-      <c r="F41" s="29">
+      <c r="F41" s="12">
         <v>49.21</v>
       </c>
-      <c r="G41" s="29">
+      <c r="G41" s="12">
         <v>41.94</v>
       </c>
-      <c r="H41" s="29">
+      <c r="H41" s="12">
         <v>45.3</v>
       </c>
-      <c r="I41" s="29">
+      <c r="I41" s="12">
         <v>38.6</v>
       </c>
-      <c r="J41" s="29">
+      <c r="J41" s="12">
         <v>54.45</v>
       </c>
-      <c r="K41" s="29">
+      <c r="K41" s="12">
         <v>56.3</v>
       </c>
-      <c r="L41" s="29">
+      <c r="L41" s="12">
         <v>52.48</v>
       </c>
     </row>
     <row r="42" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="27" t="s">
+      <c r="B42" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C42" s="30">
+      <c r="C42" s="13">
         <v>2015</v>
       </c>
-      <c r="D42" s="29">
+      <c r="D42" s="12">
         <v>29.08</v>
       </c>
-      <c r="E42" s="29">
+      <c r="E42" s="12">
         <v>26.03</v>
       </c>
-      <c r="F42" s="29">
+      <c r="F42" s="12">
         <v>32.28</v>
       </c>
-      <c r="G42" s="29">
+      <c r="G42" s="12">
         <v>22.79</v>
       </c>
-      <c r="H42" s="29">
+      <c r="H42" s="12">
         <v>19.82</v>
       </c>
-      <c r="I42" s="29">
+      <c r="I42" s="12">
         <v>25.74</v>
       </c>
-      <c r="J42" s="29">
+      <c r="J42" s="12">
         <v>30.96</v>
       </c>
-      <c r="K42" s="29">
+      <c r="K42" s="12">
         <v>27.82</v>
       </c>
-      <c r="L42" s="29">
+      <c r="L42" s="12">
         <v>34.299999999999997</v>
       </c>
     </row>
     <row r="43" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="27" t="s">
+      <c r="B43" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C43" s="30">
+      <c r="C43" s="13">
         <v>2014</v>
       </c>
-      <c r="D43" s="29">
+      <c r="D43" s="12">
         <v>19.53</v>
       </c>
-      <c r="E43" s="29">
+      <c r="E43" s="12">
         <v>20.100000000000001</v>
       </c>
-      <c r="F43" s="29">
+      <c r="F43" s="12">
         <v>18.940000000000001</v>
       </c>
-      <c r="G43" s="29">
+      <c r="G43" s="12">
         <v>34.82</v>
       </c>
-      <c r="H43" s="29">
+      <c r="H43" s="12">
         <v>34.54</v>
       </c>
-      <c r="I43" s="29">
+      <c r="I43" s="12">
         <v>35.1</v>
       </c>
-      <c r="J43" s="29">
+      <c r="J43" s="12">
         <v>14.99</v>
       </c>
-      <c r="K43" s="29">
+      <c r="K43" s="12">
         <v>15.81</v>
       </c>
-      <c r="L43" s="29">
+      <c r="L43" s="12">
         <v>14.14</v>
       </c>
     </row>
     <row r="44" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="28" t="s">
+      <c r="B44" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C44" s="30">
+      <c r="C44" s="13">
         <v>2014</v>
       </c>
-      <c r="D44" s="29">
+      <c r="D44" s="12">
         <v>53.93</v>
       </c>
-      <c r="E44" s="29">
+      <c r="E44" s="12">
         <v>55.86</v>
       </c>
-      <c r="F44" s="29">
+      <c r="F44" s="12">
         <v>51.96</v>
       </c>
-      <c r="G44" s="29">
+      <c r="G44" s="12">
         <v>43.53</v>
       </c>
-      <c r="H44" s="29">
+      <c r="H44" s="12">
         <v>46.49</v>
       </c>
-      <c r="I44" s="29">
+      <c r="I44" s="12">
         <v>40.51</v>
       </c>
-      <c r="J44" s="29">
+      <c r="J44" s="12">
         <v>57.02</v>
       </c>
-      <c r="K44" s="29">
+      <c r="K44" s="12">
         <v>58.63</v>
       </c>
-      <c r="L44" s="29">
+      <c r="L44" s="12">
         <v>55.36</v>
       </c>
     </row>
     <row r="45" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="27" t="s">
+      <c r="B45" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C45" s="30">
+      <c r="C45" s="13">
         <v>2014</v>
       </c>
-      <c r="D45" s="29">
+      <c r="D45" s="12">
         <v>26.54</v>
       </c>
-      <c r="E45" s="29">
+      <c r="E45" s="12">
         <v>24.05</v>
       </c>
-      <c r="F45" s="29">
+      <c r="F45" s="12">
         <v>29.1</v>
       </c>
-      <c r="G45" s="29">
+      <c r="G45" s="12">
         <v>21.65</v>
       </c>
-      <c r="H45" s="29">
+      <c r="H45" s="12">
         <v>18.97</v>
       </c>
-      <c r="I45" s="29">
+      <c r="I45" s="12">
         <v>24.39</v>
       </c>
-      <c r="J45" s="29">
+      <c r="J45" s="12">
         <v>27.99</v>
       </c>
-      <c r="K45" s="29">
+      <c r="K45" s="12">
         <v>25.55</v>
       </c>
-      <c r="L45" s="29">
+      <c r="L45" s="12">
         <v>30.5</v>
       </c>
     </row>
     <row r="46" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="27" t="s">
+      <c r="B46" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C46" s="30">
+      <c r="C46" s="13">
         <v>2013</v>
       </c>
-      <c r="D46" s="29">
+      <c r="D46" s="12">
         <v>19.95</v>
       </c>
-      <c r="E46" s="29">
+      <c r="E46" s="12">
         <v>20.03</v>
       </c>
-      <c r="F46" s="29">
+      <c r="F46" s="12">
         <v>19.86</v>
       </c>
-      <c r="G46" s="29">
+      <c r="G46" s="12">
         <v>33.85</v>
       </c>
-      <c r="H46" s="29">
+      <c r="H46" s="12">
         <v>32.409999999999997</v>
       </c>
-      <c r="I46" s="29">
+      <c r="I46" s="12">
         <v>35.22</v>
       </c>
-      <c r="J46" s="29">
+      <c r="J46" s="12">
         <v>15.73</v>
       </c>
-      <c r="K46" s="29">
+      <c r="K46" s="12">
         <v>16.399999999999999</v>
       </c>
-      <c r="L46" s="29">
+      <c r="L46" s="12">
         <v>15.04</v>
       </c>
     </row>
     <row r="47" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="28" t="s">
+      <c r="B47" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C47" s="30">
+      <c r="C47" s="13">
         <v>2013</v>
       </c>
-      <c r="D47" s="29">
+      <c r="D47" s="12">
         <v>55.79</v>
       </c>
-      <c r="E47" s="29">
+      <c r="E47" s="12">
         <v>56.53</v>
       </c>
-      <c r="F47" s="29">
+      <c r="F47" s="12">
         <v>55.05</v>
       </c>
-      <c r="G47" s="29">
+      <c r="G47" s="12">
         <v>45.58</v>
       </c>
-      <c r="H47" s="29">
+      <c r="H47" s="12">
         <v>48.37</v>
       </c>
-      <c r="I47" s="29">
+      <c r="I47" s="12">
         <v>42.93</v>
       </c>
-      <c r="J47" s="29">
+      <c r="J47" s="12">
         <v>58.89</v>
       </c>
-      <c r="K47" s="29">
+      <c r="K47" s="12">
         <v>58.93</v>
       </c>
-      <c r="L47" s="29">
+      <c r="L47" s="12">
         <v>58.85</v>
       </c>
     </row>
     <row r="48" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="27" t="s">
+      <c r="B48" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C48" s="30">
+      <c r="C48" s="13">
         <v>2013</v>
       </c>
-      <c r="D48" s="29">
+      <c r="D48" s="12">
         <v>24.26</v>
       </c>
-      <c r="E48" s="29">
+      <c r="E48" s="12">
         <v>23.43</v>
       </c>
-      <c r="F48" s="29">
+      <c r="F48" s="12">
         <v>25.09</v>
       </c>
-      <c r="G48" s="29">
+      <c r="G48" s="12">
         <v>20.57</v>
       </c>
-      <c r="H48" s="29">
+      <c r="H48" s="12">
         <v>19.22</v>
       </c>
-      <c r="I48" s="29">
+      <c r="I48" s="12">
         <v>21.86</v>
       </c>
-      <c r="J48" s="29">
+      <c r="J48" s="12">
         <v>25.38</v>
       </c>
-      <c r="K48" s="29">
+      <c r="K48" s="12">
         <v>24.67</v>
       </c>
-      <c r="L48" s="29">
+      <c r="L48" s="12">
         <v>26.11</v>
       </c>
     </row>
     <row r="49" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="27" t="s">
+      <c r="B49" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C49" s="30">
+      <c r="C49" s="13">
         <v>2012</v>
       </c>
-      <c r="D49" s="29">
+      <c r="D49" s="12">
         <v>19.93</v>
       </c>
-      <c r="E49" s="29">
+      <c r="E49" s="12">
         <v>20.059999999999999</v>
       </c>
-      <c r="F49" s="29">
+      <c r="F49" s="12">
         <v>19.8</v>
       </c>
-      <c r="G49" s="29">
+      <c r="G49" s="12">
         <v>37.549999999999997</v>
       </c>
-      <c r="H49" s="29">
+      <c r="H49" s="12">
         <v>35.11</v>
       </c>
-      <c r="I49" s="29">
+      <c r="I49" s="12">
         <v>39.840000000000003</v>
       </c>
-      <c r="J49" s="29">
+      <c r="J49" s="12">
         <v>14.73</v>
       </c>
-      <c r="K49" s="29">
+      <c r="K49" s="12">
         <v>15.78</v>
       </c>
-      <c r="L49" s="29">
+      <c r="L49" s="12">
         <v>13.67</v>
       </c>
     </row>
     <row r="50" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="28" t="s">
+      <c r="B50" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C50" s="30">
+      <c r="C50" s="13">
         <v>2012</v>
       </c>
-      <c r="D50" s="29">
+      <c r="D50" s="12">
         <v>55.69</v>
       </c>
-      <c r="E50" s="29">
+      <c r="E50" s="12">
         <v>56.79</v>
       </c>
-      <c r="F50" s="29">
+      <c r="F50" s="12">
         <v>54.6</v>
       </c>
-      <c r="G50" s="29">
+      <c r="G50" s="12">
         <v>44.77</v>
       </c>
-      <c r="H50" s="29">
+      <c r="H50" s="12">
         <v>49.01</v>
       </c>
-      <c r="I50" s="29">
+      <c r="I50" s="12">
         <v>40.79</v>
       </c>
-      <c r="J50" s="29">
+      <c r="J50" s="12">
         <v>58.91</v>
       </c>
-      <c r="K50" s="29">
+      <c r="K50" s="12">
         <v>59</v>
       </c>
-      <c r="L50" s="29">
+      <c r="L50" s="12">
         <v>58.82</v>
       </c>
     </row>
     <row r="51" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="27" t="s">
+      <c r="B51" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C51" s="30">
+      <c r="C51" s="13">
         <v>2012</v>
       </c>
-      <c r="D51" s="29">
+      <c r="D51" s="12">
         <v>24.38</v>
       </c>
-      <c r="E51" s="29">
+      <c r="E51" s="12">
         <v>23.15</v>
       </c>
-      <c r="F51" s="29">
+      <c r="F51" s="12">
         <v>25.6</v>
       </c>
-      <c r="G51" s="29">
+      <c r="G51" s="12">
         <v>17.68</v>
       </c>
-      <c r="H51" s="29">
+      <c r="H51" s="12">
         <v>15.88</v>
       </c>
-      <c r="I51" s="29">
+      <c r="I51" s="12">
         <v>19.37</v>
       </c>
-      <c r="J51" s="29">
+      <c r="J51" s="12">
         <v>26.36</v>
       </c>
-      <c r="K51" s="29">
+      <c r="K51" s="12">
         <v>25.22</v>
       </c>
-      <c r="L51" s="29">
+      <c r="L51" s="12">
         <v>27.51</v>
       </c>
     </row>
     <row r="52" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="27" t="s">
+      <c r="B52" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C52" s="30">
+      <c r="C52" s="13">
         <v>2011</v>
       </c>
-      <c r="D52" s="29">
+      <c r="D52" s="12">
         <v>19.59</v>
       </c>
-      <c r="E52" s="29">
+      <c r="E52" s="12">
         <v>20.45</v>
       </c>
-      <c r="F52" s="29">
+      <c r="F52" s="12">
         <v>18.73</v>
       </c>
-      <c r="G52" s="29">
+      <c r="G52" s="12">
         <v>36.04</v>
       </c>
-      <c r="H52" s="29">
+      <c r="H52" s="12">
         <v>35.869999999999997</v>
       </c>
-      <c r="I52" s="29">
+      <c r="I52" s="12">
         <v>36.21</v>
       </c>
-      <c r="J52" s="29">
+      <c r="J52" s="12">
         <v>14.82</v>
       </c>
-      <c r="K52" s="29">
+      <c r="K52" s="12">
         <v>15.94</v>
       </c>
-      <c r="L52" s="29">
+      <c r="L52" s="12">
         <v>13.71</v>
       </c>
     </row>
     <row r="53" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="28" t="s">
+      <c r="B53" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C53" s="30">
+      <c r="C53" s="13">
         <v>2011</v>
       </c>
-      <c r="D53" s="29">
+      <c r="D53" s="12">
         <v>57.59</v>
       </c>
-      <c r="E53" s="29">
+      <c r="E53" s="12">
         <v>58.22</v>
       </c>
-      <c r="F53" s="29">
+      <c r="F53" s="12">
         <v>56.97</v>
       </c>
-      <c r="G53" s="29">
+      <c r="G53" s="12">
         <v>46.69</v>
       </c>
-      <c r="H53" s="29">
+      <c r="H53" s="12">
         <v>47.69</v>
       </c>
-      <c r="I53" s="29">
+      <c r="I53" s="12">
         <v>45.69</v>
       </c>
-      <c r="J53" s="29">
+      <c r="J53" s="12">
         <v>60.75</v>
       </c>
-      <c r="K53" s="29">
+      <c r="K53" s="12">
         <v>61.29</v>
       </c>
-      <c r="L53" s="29">
+      <c r="L53" s="12">
         <v>60.21</v>
       </c>
     </row>
     <row r="54" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="27" t="s">
+      <c r="B54" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C54" s="30">
+      <c r="C54" s="13">
         <v>2011</v>
       </c>
-      <c r="D54" s="29">
+      <c r="D54" s="12">
         <v>22.82</v>
       </c>
-      <c r="E54" s="29">
+      <c r="E54" s="12">
         <v>21.33</v>
       </c>
-      <c r="F54" s="29">
+      <c r="F54" s="12">
         <v>24.3</v>
       </c>
-      <c r="G54" s="29">
+      <c r="G54" s="12">
         <v>17.27</v>
       </c>
-      <c r="H54" s="29">
+      <c r="H54" s="12">
         <v>16.440000000000001</v>
       </c>
-      <c r="I54" s="29">
+      <c r="I54" s="12">
         <v>18.100000000000001</v>
       </c>
-      <c r="J54" s="29">
+      <c r="J54" s="12">
         <v>24.43</v>
       </c>
-      <c r="K54" s="29">
+      <c r="K54" s="12">
         <v>22.76</v>
       </c>
-      <c r="L54" s="29">
+      <c r="L54" s="12">
         <v>26.08</v>
       </c>
     </row>
     <row r="55" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="27" t="s">
+      <c r="B55" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C55" s="30">
+      <c r="C55" s="13">
         <v>2005</v>
       </c>
-      <c r="D55" s="32">
+      <c r="D55" s="15">
         <v>24.154445420999647</v>
       </c>
-      <c r="E55" s="32">
+      <c r="E55" s="15">
         <v>22.719256399342001</v>
       </c>
-      <c r="F55" s="32">
+      <c r="F55" s="15">
         <v>25.605238235645007</v>
       </c>
-      <c r="G55" s="32">
+      <c r="G55" s="15">
         <v>46.854783333813693</v>
       </c>
-      <c r="H55" s="32">
+      <c r="H55" s="15">
         <v>44.052614648999509</v>
       </c>
-      <c r="I55" s="32">
+      <c r="I55" s="15">
         <v>49.656039210780335</v>
       </c>
-      <c r="J55" s="32">
+      <c r="J55" s="15">
         <v>17.627766561885203</v>
       </c>
-      <c r="K55" s="32">
+      <c r="K55" s="15">
         <v>16.629289494749859</v>
       </c>
-      <c r="L55" s="32">
+      <c r="L55" s="15">
         <v>18.640340941561153</v>
       </c>
     </row>
     <row r="56" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="28" t="s">
+      <c r="B56" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C56" s="31">
+      <c r="C56" s="14">
         <v>2005</v>
       </c>
-      <c r="D56" s="32">
+      <c r="D56" s="15">
         <v>58.914561886160612</v>
       </c>
-      <c r="E56" s="32">
+      <c r="E56" s="15">
         <v>59.518557467873897</v>
       </c>
-      <c r="F56" s="32">
+      <c r="F56" s="15">
         <v>58.303993447658122</v>
       </c>
-      <c r="G56" s="32">
+      <c r="G56" s="15">
         <v>41.525124849172229</v>
       </c>
-      <c r="H56" s="32">
+      <c r="H56" s="15">
         <v>45.554934551604795</v>
       </c>
-      <c r="I56" s="32">
+      <c r="I56" s="15">
         <v>37.49662785926138</v>
       </c>
-      <c r="J56" s="32">
+      <c r="J56" s="15">
         <v>63.914275570680147</v>
       </c>
-      <c r="K56" s="32">
+      <c r="K56" s="15">
         <v>63.504708417191956</v>
       </c>
-      <c r="L56" s="32">
+      <c r="L56" s="15">
         <v>64.329620974211139</v>
       </c>
     </row>
     <row r="57" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="27" t="s">
+      <c r="B57" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C57" s="30">
+      <c r="C57" s="13">
         <v>2005</v>
       </c>
-      <c r="D57" s="32">
+      <c r="D57" s="15">
         <v>16.930992692839745</v>
       </c>
-      <c r="E57" s="32">
+      <c r="E57" s="15">
         <v>17.762186132784088</v>
       </c>
-      <c r="F57" s="32">
+      <c r="F57" s="15">
         <v>16.090768316696874</v>
       </c>
-      <c r="G57" s="32">
+      <c r="G57" s="15">
         <v>11.620091817014073</v>
       </c>
-      <c r="H57" s="32">
+      <c r="H57" s="15">
         <v>10.392450799395696</v>
       </c>
-      <c r="I57" s="32">
+      <c r="I57" s="15">
         <v>12.847332929958288</v>
       </c>
-      <c r="J57" s="32">
+      <c r="J57" s="15">
         <v>18.457957867434651</v>
       </c>
-      <c r="K57" s="32">
+      <c r="K57" s="15">
         <v>19.866002088058185</v>
       </c>
-      <c r="L57" s="32">
+      <c r="L57" s="15">
         <v>17.030038084227709</v>
       </c>
     </row>
@@ -2631,126 +2634,126 @@
       <c r="J58" s="5"/>
     </row>
     <row r="59" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="33" t="s">
+      <c r="B59" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C59" s="28"/>
-      <c r="D59" s="28"/>
-      <c r="E59" s="28"/>
-      <c r="F59" s="28"/>
-      <c r="G59" s="28"/>
-      <c r="H59" s="28"/>
-      <c r="I59" s="28"/>
-      <c r="J59" s="28"/>
-      <c r="K59" s="28"/>
-      <c r="L59" s="28"/>
+      <c r="C59" s="11"/>
+      <c r="D59" s="11"/>
+      <c r="E59" s="11"/>
+      <c r="F59" s="11"/>
+      <c r="G59" s="11"/>
+      <c r="H59" s="11"/>
+      <c r="I59" s="11"/>
+      <c r="J59" s="11"/>
+      <c r="K59" s="11"/>
+      <c r="L59" s="11"/>
     </row>
     <row r="60" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B60" s="34" t="s">
+      <c r="B60" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="C60" s="34"/>
-      <c r="D60" s="34"/>
-      <c r="E60" s="34"/>
-      <c r="F60" s="34"/>
-      <c r="G60" s="34"/>
-      <c r="H60" s="34"/>
-      <c r="I60" s="34"/>
-      <c r="J60" s="34"/>
-      <c r="K60" s="34"/>
-      <c r="L60" s="34"/>
+      <c r="C60" s="22"/>
+      <c r="D60" s="22"/>
+      <c r="E60" s="22"/>
+      <c r="F60" s="22"/>
+      <c r="G60" s="22"/>
+      <c r="H60" s="22"/>
+      <c r="I60" s="22"/>
+      <c r="J60" s="22"/>
+      <c r="K60" s="22"/>
+      <c r="L60" s="22"/>
     </row>
     <row r="61" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B61" s="34" t="s">
+      <c r="B61" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="C61" s="34"/>
-      <c r="D61" s="34"/>
-      <c r="E61" s="34"/>
-      <c r="F61" s="34"/>
-      <c r="G61" s="34"/>
-      <c r="H61" s="34"/>
-      <c r="I61" s="34"/>
-      <c r="J61" s="34"/>
-      <c r="K61" s="34"/>
-      <c r="L61" s="34"/>
-    </row>
-    <row r="62" spans="2:12" s="35" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="34" t="s">
+      <c r="C61" s="22"/>
+      <c r="D61" s="22"/>
+      <c r="E61" s="22"/>
+      <c r="F61" s="22"/>
+      <c r="G61" s="22"/>
+      <c r="H61" s="22"/>
+      <c r="I61" s="22"/>
+      <c r="J61" s="22"/>
+      <c r="K61" s="22"/>
+      <c r="L61" s="22"/>
+    </row>
+    <row r="62" spans="2:12" s="17" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="C62" s="34"/>
-      <c r="D62" s="34"/>
-      <c r="E62" s="34"/>
-      <c r="F62" s="34"/>
-      <c r="G62" s="34"/>
-      <c r="H62" s="34"/>
-      <c r="I62" s="34"/>
-      <c r="J62" s="34"/>
-      <c r="K62" s="34"/>
-      <c r="L62" s="34"/>
+      <c r="C62" s="22"/>
+      <c r="D62" s="22"/>
+      <c r="E62" s="22"/>
+      <c r="F62" s="22"/>
+      <c r="G62" s="22"/>
+      <c r="H62" s="22"/>
+      <c r="I62" s="22"/>
+      <c r="J62" s="22"/>
+      <c r="K62" s="22"/>
+      <c r="L62" s="22"/>
     </row>
     <row r="63" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="36" t="s">
+      <c r="B63" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C63" s="37"/>
-      <c r="D63" s="37"/>
-      <c r="E63" s="37"/>
-      <c r="F63" s="37"/>
-      <c r="G63" s="37"/>
-      <c r="H63" s="37"/>
-      <c r="I63" s="37"/>
-      <c r="J63" s="37"/>
-      <c r="K63" s="37"/>
-      <c r="L63" s="37"/>
+      <c r="C63" s="19"/>
+      <c r="D63" s="19"/>
+      <c r="E63" s="19"/>
+      <c r="F63" s="19"/>
+      <c r="G63" s="19"/>
+      <c r="H63" s="19"/>
+      <c r="I63" s="19"/>
+      <c r="J63" s="19"/>
+      <c r="K63" s="19"/>
+      <c r="L63" s="19"/>
     </row>
     <row r="64" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="37"/>
-      <c r="C64" s="37"/>
-      <c r="D64" s="37"/>
-      <c r="E64" s="37"/>
-      <c r="F64" s="37"/>
-      <c r="G64" s="37"/>
-      <c r="H64" s="37"/>
-      <c r="I64" s="37"/>
-      <c r="J64" s="37"/>
-      <c r="K64" s="37"/>
-      <c r="L64" s="37"/>
+      <c r="B64" s="19"/>
+      <c r="C64" s="19"/>
+      <c r="D64" s="19"/>
+      <c r="E64" s="19"/>
+      <c r="F64" s="19"/>
+      <c r="G64" s="19"/>
+      <c r="H64" s="19"/>
+      <c r="I64" s="19"/>
+      <c r="J64" s="19"/>
+      <c r="K64" s="19"/>
+      <c r="L64" s="19"/>
     </row>
     <row r="65" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="37" t="s">
+      <c r="B65" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C65" s="37"/>
-      <c r="D65" s="37"/>
-      <c r="E65" s="37"/>
-      <c r="F65" s="37"/>
-      <c r="G65" s="37"/>
-      <c r="H65" s="37"/>
-      <c r="I65" s="37"/>
-      <c r="J65" s="37"/>
-      <c r="K65" s="37"/>
-      <c r="L65" s="37"/>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="19"/>
+      <c r="K65" s="19"/>
+      <c r="L65" s="19"/>
     </row>
     <row r="66" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="67" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="38" t="s">
+      <c r="B67" s="20" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="68" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="38" t="s">
+      <c r="B68" s="20" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="69" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="38" t="s">
+      <c r="B69" s="20" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="70" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="36" t="s">
+      <c r="B70" s="18" t="s">
         <v>23</v>
       </c>
     </row>
